--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1738,7 +1738,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4358-163-CM26</t>
+          <t>188-507-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7061.04</v>
+        <v>34153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>188-507-CM26</t>
+          <t>4177-92-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>34153</v>
+        <v>8769.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4177-92-CM26</t>
+          <t>3997-306-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8769.74</v>
+        <v>14635.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3997-306-CM26</t>
+          <t>1271178-266-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,32 +1941,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14635.93</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1271178-266-CM26</t>
+          <t>1237849-145-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>65.081.056-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1479.16</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1237849-145-CM26</t>
+          <t>1750-284-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.081.056-2</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO COMUNAL Y PRODUCTIVO DE LA FLORIDA</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3077.1</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1750-284-CM26</t>
+          <t>937232-578-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46156.53</v>
+        <v>2112.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>937232-578-CM26</t>
+          <t>1078177-724-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2185,32 +2185,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2112.87</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1078177-724-CM26</t>
+          <t>4193-366-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,37 +2241,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2113.08</v>
+        <v>53273.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4193-366-CM26</t>
+          <t>4494-608-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2312,27 +2312,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>53273.68</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4494-608-CM26</t>
+          <t>1287766-76-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>65.199.980-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>35481.04</v>
+        <v>4080.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1287766-76-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2429,17 +2429,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.199.980-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Ñuñoa</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4080.32</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="34">
@@ -2531,7 +2531,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>872535-246-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2556,27 +2556,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7909.38</v>
+        <v>49233.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>872535-246-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2612,32 +2612,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>49233.63</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>836-127-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,37 +2668,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1422.05</v>
+        <v>46156.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>836-127-CM26</t>
+          <t>1723-493-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,27 +2739,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46156.53</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1723-493-CM26</t>
+          <t>857-121-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,27 +2800,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1056.54</v>
+        <v>50772.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>857-121-CM26</t>
+          <t>751-300-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,27 +2861,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>50772.18</v>
+        <v>21124.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>751-300-CM26</t>
+          <t>4246-85-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.976.100-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21124.88</v>
+        <v>21128.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4246-85-CM26</t>
+          <t>881-232-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2983,27 +2983,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.976.100-6</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>21128.69</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>881-232-CM26</t>
+          <t>1375746-102-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3044,27 +3044,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1547</v>
+        <v>16260.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1375746-102-CM26</t>
+          <t>688-100-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16260.16</v>
+        <v>71574.92999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>688-100-CM26</t>
+          <t>514862-530-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>71574.92999999999</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>514862-530-CM26</t>
+          <t>4170-239-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,27 +3227,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1901.77</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="47">
@@ -3385,7 +3385,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4170-239-CM26</t>
+          <t>4323-198-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>30771.02</v>
+        <v>1056.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4323-198-CM26</t>
+          <t>1079713-481-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3471,17 +3471,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079713-481-CM26</t>
+          <t>188-517-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,22 +3522,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1056.54</v>
+        <v>5810.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>188-517-CM26</t>
+          <t>1375761-1560-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3588,32 +3588,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5810.39</v>
+        <v>12757.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1375761-1560-CM26</t>
+          <t>5019-215-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,27 +3654,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>12757.4</v>
+        <v>1267.85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5019-215-CM26</t>
+          <t>1147293-240-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1267.85</v>
+        <v>17915.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1147293-240-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17915.39</v>
+        <v>17475.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,27 +3837,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>17475.15</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3938,7 +3938,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3978,22 +3978,26 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="59">
@@ -4182,7 +4186,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>1057508-2275-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4202,106 +4206,41 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>224910</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1057508-2275-CM26</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>61.607.000-2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="n">
         <v>827.24</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1923,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1988,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2053,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2118,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2183,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2248,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2313,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2378,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2443,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2508,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2573,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2638,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2703,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2768,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2833,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2898,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2963,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3028,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3093,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3219,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3284,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3349,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3414,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3479,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3544,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3609,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3674,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3739,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3804,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3869,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3934,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3999,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3812,7 +4016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>1175-708-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3832,22 +4036,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3860,20 +4064,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>132839.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1175-708-CM26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3893,22 +4101,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3932,13 +4140,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>132839.7</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>624-187-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3963,27 +4171,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3997,13 +4205,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>224910</v>
+        <v>7868.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>624-187-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4028,43 +4236,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7868.52</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3428-231-CM26</t>
+          <t>1057508-2275-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4089,43 +4301,47 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1690.47</v>
+        <v>827.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4414-1161-CM26</t>
+          <t>3428-231-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4145,48 +4361,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>29687.88</v>
+        <v>1690.47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057508-2275-CM26</t>
+          <t>4414-1161-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4206,42 +4426,111 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.160.100-5</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>29687.88</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>858-348-SE26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>61.607.000-2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>827.24</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>713286</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2525,7 +2525,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1121-84-CM26</t>
+          <t>1393575-77-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7909.38</v>
+        <v>1422.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1121-83-CM26</t>
+          <t>1121-84-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>30913.52</v>
+        <v>7909.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>872535-246-CM26</t>
+          <t>1121-83-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2680,27 +2680,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2714,13 +2714,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>49233.63</v>
+        <v>30913.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1393575-77-CM26</t>
+          <t>872535-246-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1422.05</v>
+        <v>49233.63</v>
       </c>
     </row>
     <row r="37">
@@ -3366,7 +3366,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4170-239-CM26</t>
+          <t>1202333-127-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3391,32 +3391,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.060.700-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>30771.02</v>
+        <v>27892.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1202333-127-CM26</t>
+          <t>4170-239-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3456,32 +3456,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.060.700-K</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>27892.7</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="48">
@@ -3951,7 +3951,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5066-202-CM26</t>
+          <t>1260-126-SE26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3971,37 +3971,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Extranjero</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17475.15</v>
+        <v>106407.42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1175-708-CM26</t>
+          <t>5066-202-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4031,22 +4031,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4075,13 +4075,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>132839.7</v>
+        <v>17475.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2412-522-CM26</t>
+          <t>1175-708-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4101,22 +4101,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4140,13 +4140,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>74764.49000000001</v>
+        <v>132839.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>624-187-CM26</t>
+          <t>2412-522-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4171,27 +4171,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7868.52</v>
+        <v>74764.49000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>867990-485-CM26</t>
+          <t>1057508-2275-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4270,13 +4270,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>224910</v>
+        <v>827.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057508-2275-CM26</t>
+          <t>3428-231-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4301,32 +4301,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>827.24</v>
+        <v>1690.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3428-231-CM26</t>
+          <t>4414-1161-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4361,37 +4361,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1690.47</v>
+        <v>29687.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4414-1161-CM26</t>
+          <t>867990-485-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4431,27 +4431,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4465,71 +4465,136 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>29687.88</v>
+        <v>224910</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>624-187-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>7868.52</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>858-348-SE26</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>61.107.000-4</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="n">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>713286</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ago-2026.xlsx
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
